--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696BE575-E26B-49FF-9591-9177886705BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C460E7-0FB6-4A0E-A447-25B1DB86F0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,12 @@
   </si>
   <si>
     <t xml:space="preserve">Had a very good and productive day and the level of energy was also kinda good but the was also very tiering </t>
+  </si>
+  <si>
+    <t>Had a very low feeling day I was not even feeloing well not done anything productive and not even feeling well.</t>
+  </si>
+  <si>
+    <t>Togay I had a very productive day and I was also studying for a while I did revise few topic hada good day</t>
   </si>
 </sst>
 </file>
@@ -2158,48 +2164,96 @@
       </c>
     </row>
     <row r="28" spans="1:25" ht="93" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B28" s="14">
+        <v>500</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>0</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>300</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="29" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B29" s="14">
+        <v>500</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>320</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>300</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="30" spans="1:25" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C460E7-0FB6-4A0E-A447-25B1DB86F0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39781551-B1B3-40C4-92DF-17EB394742AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -288,7 +288,10 @@
     <t>Had a very low feeling day I was not even feeloing well not done anything productive and not even feeling well.</t>
   </si>
   <si>
-    <t>Togay I had a very productive day and I was also studying for a while I did revise few topic hada good day</t>
+    <t>Today I had a very productive day and I was also studying for a while I did revise few topic hada good day</t>
+  </si>
+  <si>
+    <t>Today had a very hectic and productive day and it was very good  I was also feeling very good thorughout the day and the day went well.</t>
   </si>
 </sst>
 </file>
@@ -2256,26 +2259,50 @@
       </c>
     </row>
     <row r="30" spans="1:25" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B30" s="14">
+        <v>400</v>
+      </c>
+      <c r="C30" s="14">
+        <v>90</v>
+      </c>
+      <c r="D30" s="14">
+        <v>320</v>
+      </c>
+      <c r="E30" s="14">
+        <v>60</v>
+      </c>
+      <c r="F30" s="14">
+        <v>300</v>
+      </c>
+      <c r="G30" s="14">
+        <v>6</v>
+      </c>
+      <c r="H30" s="14">
+        <v>100</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>170</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="31" spans="1:25" ht="102.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39781551-B1B3-40C4-92DF-17EB394742AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9110DBA3-A97E-449C-9C22-5C45DE11E663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>Today had a very hectic and productive day and it was very good  I was also feeling very good thorughout the day and the day went well.</t>
+  </si>
+  <si>
+    <t>Today was a productive day. I focused well on my studies and coding, attended my classes, and also made time for other activities. I felt good overall, although my energy was moderate. I stayed consistent with my work and ended the day feeling satisfied.</t>
   </si>
 </sst>
 </file>
@@ -2304,27 +2307,51 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="102.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+    <row r="31" spans="1:25" ht="144.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B31" s="14">
+        <v>450</v>
+      </c>
+      <c r="C31" s="14">
+        <v>60</v>
+      </c>
+      <c r="D31" s="14">
+        <v>350</v>
+      </c>
+      <c r="E31" s="14">
+        <v>30</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>200</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="32" spans="1:25" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9110DBA3-A97E-449C-9C22-5C45DE11E663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CD8BA6-B1A5-42FE-8B51-5C5229A6E760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>Today was a productive day. I focused well on my studies and coding, attended my classes, and also made time for other activities. I felt good overall, although my energy was moderate. I stayed consistent with my work and ended the day feeling satisfied.</t>
+  </si>
+  <si>
+    <t>Today was a decent day.Imearged to stay focused on my studies and coding . I attened my classes and completed most of what I planned . Enengy was a little low, but I still stayed consistent.</t>
   </si>
 </sst>
 </file>
@@ -2353,27 +2356,51 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+    <row r="32" spans="1:25" ht="128.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>50</v>
+      </c>
+      <c r="D32" s="14">
+        <v>350</v>
+      </c>
+      <c r="E32" s="14">
+        <v>50</v>
+      </c>
+      <c r="F32" s="14">
+        <v>250</v>
+      </c>
+      <c r="G32" s="14">
+        <v>5</v>
+      </c>
+      <c r="H32" s="14">
+        <v>200</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="33" spans="1:14" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CD8BA6-B1A5-42FE-8B51-5C5229A6E760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE59987-C2AA-4612-8A59-A3082B301A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,12 @@
   </si>
   <si>
     <t>Today was a decent day.Imearged to stay focused on my studies and coding . I attened my classes and completed most of what I planned . Enengy was a little low, but I still stayed consistent.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Today was our freshers party and honestly it was such a fun and memorable day and apart from this I hada good and satitisfied chill kinda a day.</t>
   </si>
 </sst>
 </file>
@@ -1578,7 +1584,7 @@
         <v>320</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="L15" s="16" t="s">
         <v>50</v>
@@ -2114,7 +2120,7 @@
         <v>320</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="L26" s="16" t="s">
         <v>50</v>
@@ -2402,27 +2408,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+    <row r="33" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B33" s="14">
+        <v>450</v>
+      </c>
+      <c r="C33" s="14">
+        <v>60</v>
+      </c>
+      <c r="D33" s="14">
+        <v>50</v>
+      </c>
+      <c r="E33" s="14">
+        <v>20</v>
+      </c>
+      <c r="F33" s="14">
+        <v>100</v>
+      </c>
+      <c r="G33" s="14">
+        <v>2</v>
+      </c>
+      <c r="H33" s="14">
+        <v>300</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="34" spans="1:14" ht="116.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>
@@ -2446,7 +2476,7 @@
       <c r="M34" s="16"/>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:14" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE59987-C2AA-4612-8A59-A3082B301A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD116E7-9D3D-43F6-8283-4D8B7E4C251D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t>Today was our freshers party and honestly it was such a fun and memorable day and apart from this I hada good and satitisfied chill kinda a day.</t>
+  </si>
+  <si>
+    <t>It was a good and productive day. I attended my classes and spent time studying and working on my tasks. I felt satisfied with how the day went, although I was a little tired by the end. Overall, it was a decent and balanced day</t>
   </si>
 </sst>
 </file>
@@ -2454,29 +2457,53 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="116.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+    <row r="34" spans="1:14" ht="129" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B34" s="14">
+        <v>400</v>
+      </c>
+      <c r="C34" s="14">
+        <v>50</v>
+      </c>
+      <c r="D34" s="14">
+        <v>60</v>
+      </c>
+      <c r="E34" s="14">
+        <v>30</v>
+      </c>
+      <c r="F34" s="14">
+        <v>350</v>
+      </c>
+      <c r="G34" s="14">
+        <v>7</v>
+      </c>
+      <c r="H34" s="14">
+        <v>250</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD116E7-9D3D-43F6-8283-4D8B7E4C251D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BA53CD-9807-41D9-823B-885E88651EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>It was a good and productive day. I attended my classes and spent time studying and working on my tasks. I felt satisfied with how the day went, although I was a little tired by the end. Overall, it was a decent and balanced day</t>
+  </si>
+  <si>
+    <t>It was a good productive day I attended my classes and spent time stydung wans watching movie alsoalso did  done cooking and had a very god day.</t>
   </si>
 </sst>
 </file>
@@ -2504,26 +2507,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46092</v>
+      </c>
+      <c r="B35" s="14">
+        <v>450</v>
+      </c>
+      <c r="C35" s="14">
+        <v>60</v>
+      </c>
+      <c r="D35" s="14">
+        <v>60</v>
+      </c>
+      <c r="E35" s="14">
+        <v>60</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>350</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="36" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BA53CD-9807-41D9-823B-885E88651EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A618F5-FE51-4D66-86A8-6947323D27B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -310,6 +310,12 @@
   </si>
   <si>
     <t>It was a good productive day I attended my classes and spent time stydung wans watching movie alsoalso did  done cooking and had a very god day.</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>had a very good and chill day becoz I woke up late and had a satisfied day.</t>
   </si>
 </sst>
 </file>
@@ -2508,7 +2514,7 @@
     </row>
     <row r="35" spans="1:14" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13">
-        <v>46092</v>
+        <v>46276</v>
       </c>
       <c r="B35" s="14">
         <v>450</v>
@@ -2553,26 +2559,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B36" s="14">
+        <v>500</v>
+      </c>
+      <c r="C36" s="14">
+        <v>40</v>
+      </c>
+      <c r="D36" s="14">
+        <v>60</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14">
+        <v>400</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A618F5-FE51-4D66-86A8-6947323D27B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC23CAD-2E05-4D31-9AEA-9C028957EADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -315,7 +315,10 @@
     <t>Very Satisfied</t>
   </si>
   <si>
-    <t>had a very good and chill day becoz I woke up late and had a satisfied day.</t>
+    <t>Had a very good and chill day becoz I woke up late and had a satisfied day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Had a very nice a a bit productive day also enjoyed the day very much </t>
   </si>
 </sst>
 </file>
@@ -2468,7 +2471,7 @@
     </row>
     <row r="34" spans="1:14" ht="129" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="13">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B34" s="14">
         <v>400</v>
@@ -2514,7 +2517,7 @@
     </row>
     <row r="35" spans="1:14" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B35" s="14">
         <v>450</v>
@@ -2558,9 +2561,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B36" s="14">
         <v>500</v>
@@ -2604,27 +2607,51 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+    <row r="37" spans="1:14" ht="91.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B37" s="14">
+        <v>420</v>
+      </c>
+      <c r="C37" s="14">
+        <v>50</v>
+      </c>
+      <c r="D37" s="14">
+        <v>50</v>
+      </c>
+      <c r="E37" s="14">
+        <v>30</v>
+      </c>
+      <c r="F37" s="14">
+        <v>200</v>
+      </c>
+      <c r="G37" s="14">
+        <v>4</v>
+      </c>
+      <c r="H37" s="14">
+        <v>200</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC23CAD-2E05-4D31-9AEA-9C028957EADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40829E87-37D7-4726-AB03-301EA2B5168D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t xml:space="preserve">Had a very nice a a bit productive day also enjoyed the day very much </t>
+  </si>
+  <si>
+    <t>Today I was not feeling well did not had a good and I took rest not done anything productive.</t>
   </si>
 </sst>
 </file>
@@ -2607,7 +2610,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="91.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13">
         <v>46279</v>
       </c>
@@ -2653,27 +2656,51 @@
         <v>93</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+    <row r="38" spans="1:14" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B38" s="14">
+        <v>550</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>0</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>150</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>740</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40829E87-37D7-4726-AB03-301EA2B5168D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1D71C4-DF73-4E9D-BA5D-5410DDE05AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>Today I was not feeling well did not had a good and I took rest not done anything productive.</t>
+  </si>
+  <si>
+    <t>Today I had a low-energy day and was not feeling very productive. I mostly rested and didn’t do much.</t>
   </si>
 </sst>
 </file>
@@ -2702,27 +2705,51 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+    <row r="39" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B39" s="14">
+        <v>500</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>0</v>
+      </c>
+      <c r="E39" s="14">
+        <v>0</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>200</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>740</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1D71C4-DF73-4E9D-BA5D-5410DDE05AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06345CE9-BE84-47C6-AD1C-D6FC7B8D39E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>Today I had a low-energy day and was not feeling very productive. I mostly rested and didn’t do much.</t>
+  </si>
+  <si>
+    <t>Today I was in a very good mood and also also feeling better and hada kinda a active day from pat two days.</t>
   </si>
 </sst>
 </file>
@@ -2751,27 +2754,51 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+    <row r="40" spans="1:14" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B40" s="14">
+        <v>350</v>
+      </c>
+      <c r="C40" s="14">
+        <v>50</v>
+      </c>
+      <c r="D40" s="14">
+        <v>60</v>
+      </c>
+      <c r="E40" s="14">
+        <v>30</v>
+      </c>
+      <c r="F40" s="14">
+        <v>350</v>
+      </c>
+      <c r="G40" s="14">
+        <v>7</v>
+      </c>
+      <c r="H40" s="14">
+        <v>250</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06345CE9-BE84-47C6-AD1C-D6FC7B8D39E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A147C10E-2386-4038-9247-75F9AD570903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>Today I was in a very good mood and also also feeling better and hada kinda a active day from pat two days.</t>
+  </si>
+  <si>
+    <t>Today I had a productive day and also kinda hectic too I was also studying and also done some extra things to too I was in good mood and kinda satisfied.</t>
   </si>
 </sst>
 </file>
@@ -2800,29 +2803,53 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+    <row r="41" spans="1:14" ht="96" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B41" s="14">
+        <v>300</v>
+      </c>
+      <c r="C41" s="14">
+        <v>50</v>
+      </c>
+      <c r="D41" s="14">
+        <v>300</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>350</v>
+      </c>
+      <c r="G41" s="14">
+        <v>7</v>
+      </c>
+      <c r="H41" s="14">
+        <v>250</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
@@ -2844,7 +2871,7 @@
       <c r="M42" s="16"/>
       <c r="N42" s="17"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A147C10E-2386-4038-9247-75F9AD570903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0474A5-2CE2-41FA-9DE8-21BB69A47C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -207,9 +207,6 @@
     <t>CAP-776</t>
   </si>
   <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>Neutral</t>
   </si>
   <si>
@@ -331,6 +328,12 @@
   </si>
   <si>
     <t>Today I had a productive day and also kinda hectic too I was also studying and also done some extra things to too I was in good mood and kinda satisfied.</t>
+  </si>
+  <si>
+    <t>Sept</t>
+  </si>
+  <si>
+    <t>Today was a good day. I got enough sleep and also spent some time on fitness. I studied for a while and took some time to relax and do other activities. Overall, I felt good and had high energy, although I think I could have been more productive with my study time.</t>
   </si>
 </sst>
 </file>
@@ -1093,7 +1096,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="G3" s="26"/>
     </row>
@@ -1245,10 +1248,10 @@
         <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="23" t="s">
         <v>59</v>
-      </c>
-      <c r="N7" s="23" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -1288,13 +1291,13 @@
         <v>49</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N8" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O8" s="19"/>
       <c r="P8" s="19"/>
@@ -1335,16 +1338,16 @@
         <v>415</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N9" s="22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1381,7 +1384,7 @@
         <v>320</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L10" s="16" t="s">
         <v>50</v>
@@ -1390,7 +1393,7 @@
         <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="88.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1430,13 +1433,13 @@
         <v>49</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M11" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1473,16 +1476,16 @@
         <v>245</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L12" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N12" s="22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1519,16 +1522,16 @@
         <v>110</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L13" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N13" s="22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -1565,16 +1568,16 @@
         <v>450</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="78" customHeight="1" x14ac:dyDescent="0.3">
@@ -1611,16 +1614,16 @@
         <v>320</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L15" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N15" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O15" s="20"/>
       <c r="P15" s="20"/>
@@ -1668,13 +1671,13 @@
         <v>49</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N16" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O16" s="18"/>
       <c r="P16" s="18"/>
@@ -1725,13 +1728,13 @@
         <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N17" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O17" s="18"/>
       <c r="P17" s="18"/>
@@ -1788,7 +1791,7 @@
         <v>50</v>
       </c>
       <c r="N18" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:25" ht="76.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1825,16 +1828,16 @@
         <v>410</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N19" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:25" ht="91.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1871,16 +1874,16 @@
         <v>400</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M20" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N20" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1917,16 +1920,16 @@
         <v>720</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N21" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:25" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1963,16 +1966,16 @@
         <v>790</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L22" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" s="22" t="s">
         <v>75</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="N22" s="22" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="84" customHeight="1" x14ac:dyDescent="0.3">
@@ -2009,16 +2012,16 @@
         <v>660</v>
       </c>
       <c r="K23" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M23" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L23" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="M23" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N23" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -2055,16 +2058,16 @@
         <v>410</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M24" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="82.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2101,16 +2104,16 @@
         <v>330</v>
       </c>
       <c r="K25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L25" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M25" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N25" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:25" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -2147,16 +2150,16 @@
         <v>320</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L26" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:25" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2202,7 +2205,7 @@
         <v>51</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="93" customHeight="1" x14ac:dyDescent="0.3">
@@ -2239,16 +2242,16 @@
         <v>640</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M28" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N28" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.3">
@@ -2285,7 +2288,7 @@
         <v>290</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L29" s="16" t="s">
         <v>50</v>
@@ -2294,7 +2297,7 @@
         <v>51</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:25" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2340,7 +2343,7 @@
         <v>51</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="144.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2380,13 +2383,13 @@
         <v>49</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M31" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:25" ht="128.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2429,10 +2432,10 @@
         <v>50</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="105" customHeight="1" x14ac:dyDescent="0.3">
@@ -2469,16 +2472,16 @@
         <v>460</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L33" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="129" customHeight="1" x14ac:dyDescent="0.3">
@@ -2524,7 +2527,7 @@
         <v>51</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2570,7 +2573,7 @@
         <v>51</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="69" customHeight="1" x14ac:dyDescent="0.3">
@@ -2610,13 +2613,13 @@
         <v>49</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M36" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -2662,7 +2665,7 @@
         <v>51</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="66" customHeight="1" x14ac:dyDescent="0.3">
@@ -2699,16 +2702,16 @@
         <v>740</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L38" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M38" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M38" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N38" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.3">
@@ -2745,16 +2748,16 @@
         <v>740</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2791,7 +2794,7 @@
         <v>350</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L40" s="16" t="s">
         <v>50</v>
@@ -2800,7 +2803,7 @@
         <v>51</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="96" customHeight="1" x14ac:dyDescent="0.3">
@@ -2846,30 +2849,54 @@
         <v>51</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="163.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B42" s="14">
+        <v>450</v>
+      </c>
+      <c r="C42" s="14">
+        <v>60</v>
+      </c>
+      <c r="D42" s="14">
+        <v>50</v>
+      </c>
+      <c r="E42" s="14">
+        <v>0</v>
+      </c>
+      <c r="F42" s="14">
+        <v>0</v>
+      </c>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>350</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="43" spans="1:14" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0474A5-2CE2-41FA-9DE8-21BB69A47C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE775294-6948-4A1F-96C4-63A9054C6268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>Today was a good day. I got enough sleep and also spent some time on fitness. I studied for a while and took some time to relax and do other activities. Overall, I felt good and had high energy, although I think I could have been more productive with my study time.</t>
+  </si>
+  <si>
+    <t>Today was a good day. I got enough sleep and also spent some time on fitness. I studied for a while and took some time to relax and do other activities. Overall, I felt good and had enough energy, although I think I could have been more productive with my study time</t>
   </si>
 </sst>
 </file>
@@ -2898,29 +2901,53 @@
         <v>98</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+    <row r="43" spans="1:14" ht="156.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B43" s="14">
+        <v>500</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>0</v>
+      </c>
+      <c r="E43" s="14">
+        <v>20</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>300</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+        <v>620</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE775294-6948-4A1F-96C4-63A9054C6268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC45423-866B-424A-8F68-A9EB54E3A0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -337,6 +337,9 @@
   </si>
   <si>
     <t>Today was a good day. I got enough sleep and also spent some time on fitness. I studied for a while and took some time to relax and do other activities. Overall, I felt good and had enough energy, although I think I could have been more productive with my study time</t>
+  </si>
+  <si>
+    <t>Today I had a very good and energetic day also did something productive and it was good day .</t>
   </si>
 </sst>
 </file>
@@ -2948,26 +2951,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B44" s="14">
+        <v>400</v>
+      </c>
+      <c r="C44" s="14">
+        <v>35</v>
+      </c>
+      <c r="D44" s="14">
+        <v>60</v>
+      </c>
+      <c r="E44" s="14">
+        <v>20</v>
+      </c>
+      <c r="F44" s="14">
+        <v>200</v>
+      </c>
+      <c r="G44" s="14">
+        <v>4</v>
+      </c>
+      <c r="H44" s="14">
+        <v>300</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1015</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>425</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC45423-866B-424A-8F68-A9EB54E3A0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7888BD-72A6-4C6B-B30C-317C9624F80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -340,6 +340,9 @@
   </si>
   <si>
     <t>Today I had a very good and energetic day also did something productive and it was good day .</t>
+  </si>
+  <si>
+    <t>Today was a very good and productive day. I attended all my classes and spent a good amount of time studying. I also worked on coding and other activities. I felt energetic and satisfied with my day, although I could have been a little more productive.</t>
   </si>
 </sst>
 </file>
@@ -2950,7 +2953,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="76.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="13">
         <v>46286</v>
       </c>
@@ -2996,29 +2999,53 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+    <row r="45" spans="1:14" ht="141.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B45" s="14">
+        <v>450</v>
+      </c>
+      <c r="C45" s="14">
+        <v>40</v>
+      </c>
+      <c r="D45" s="14">
+        <v>90</v>
+      </c>
+      <c r="E45" s="14">
+        <v>20</v>
+      </c>
+      <c r="F45" s="14">
+        <v>250</v>
+      </c>
+      <c r="G45" s="14">
+        <v>5</v>
+      </c>
+      <c r="H45" s="14">
+        <v>200</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+        <v>390</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -3040,7 +3067,7 @@
       <c r="M46" s="16"/>
       <c r="N46" s="17"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -3062,7 +3089,7 @@
       <c r="M47" s="16"/>
       <c r="N47" s="17"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -3084,7 +3111,7 @@
       <c r="M48" s="16"/>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -3106,7 +3133,7 @@
       <c r="M49" s="16"/>
       <c r="N49" s="17"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -3128,7 +3155,7 @@
       <c r="M50" s="16"/>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7888BD-72A6-4C6B-B30C-317C9624F80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57090E3D-6661-4B94-9746-07FEDAAC634A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>Today was a very good and productive day. I attended all my classes and spent a good amount of time studying. I also worked on coding and other activities. I felt energetic and satisfied with my day, although I could have been a little more productive.</t>
+  </si>
+  <si>
+    <t>Today it was a kinda a low feeling day and I was not that active and also did not do that much productive .</t>
   </si>
 </sst>
 </file>
@@ -3046,26 +3049,50 @@
       </c>
     </row>
     <row r="46" spans="1:14" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B46" s="14">
+        <v>400</v>
+      </c>
+      <c r="C46" s="14">
+        <v>40</v>
+      </c>
+      <c r="D46" s="14">
+        <v>60</v>
+      </c>
+      <c r="E46" s="14">
+        <v>50</v>
+      </c>
+      <c r="F46" s="14">
+        <v>250</v>
+      </c>
+      <c r="G46" s="14">
+        <v>5</v>
+      </c>
+      <c r="H46" s="14">
+        <v>250</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="47" spans="1:14" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>
